--- a/data/trans_orig/IP35-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP35-Estudios-trans_orig.xlsx
@@ -1637,12 +1637,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>65136</t>
+          <t>64626</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>78147</t>
+          <t>77113</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55907</t>
+          <t>56101</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68809</t>
+          <t>69451</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,12 +1707,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>125186</t>
+          <t>124701</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>142764</t>
+          <t>143705</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,86%</t>
         </is>
       </c>
     </row>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9491</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20942</t>
+          <t>20849</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,12 +1785,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>15508</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28943</t>
+          <t>28636</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28429</t>
+          <t>27192</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45512</t>
+          <t>44880</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8485</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11438</t>
+          <t>11238</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -2545,12 +2545,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>46331</t>
+          <t>45044</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68995</t>
+          <t>68118</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45692</t>
+          <t>44555</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67542</t>
+          <t>66331</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>97984</t>
+          <t>97260</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>129327</t>
+          <t>127205</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -2658,12 +2658,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>53869</t>
+          <t>53382</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>76261</t>
+          <t>76726</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2673,12 +2673,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52859</t>
+          <t>52491</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>76839</t>
+          <t>76055</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2708,12 +2708,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>110222</t>
+          <t>110043</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>144352</t>
+          <t>143187</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2743,12 +2743,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -2771,12 +2771,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26894</t>
+          <t>27151</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45239</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35951</t>
+          <t>35679</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56887</t>
+          <t>57031</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67909</t>
+          <t>67951</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>94464</t>
+          <t>94745</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -2884,12 +2884,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>203616</t>
+          <t>202572</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>236210</t>
+          <t>235813</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2899,12 +2899,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>246740</t>
+          <t>245238</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>281372</t>
+          <t>280588</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>460045</t>
+          <t>460695</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>507283</t>
+          <t>508923</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>57,02%</t>
         </is>
       </c>
     </row>
@@ -2997,12 +2997,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29557</t>
+          <t>29667</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48501</t>
+          <t>48939</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>34475</t>
+          <t>34974</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>55393</t>
+          <t>56001</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,12 +3067,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>69112</t>
+          <t>69589</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>97208</t>
+          <t>99855</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4314</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,12 +3145,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>7771</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,12 +3180,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3679,12 +3679,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>56229</t>
+          <t>55331</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>76177</t>
+          <t>76678</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3694,12 +3694,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>53214</t>
+          <t>53383</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>73337</t>
+          <t>74024</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>114741</t>
+          <t>115867</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>143157</t>
+          <t>143925</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,32%</t>
         </is>
       </c>
     </row>
@@ -3792,12 +3792,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>58368</t>
+          <t>57295</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>78379</t>
+          <t>78730</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>46075</t>
+          <t>46353</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>66235</t>
+          <t>65763</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>108427</t>
+          <t>108423</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>136037</t>
+          <t>136916</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,21%</t>
         </is>
       </c>
     </row>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6766</t>
+          <t>6699</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>16736</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3920,12 +3920,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>21013</t>
+          <t>21598</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>18567</t>
+          <t>18172</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>34749</t>
+          <t>34256</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -4018,12 +4018,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>14967</t>
+          <t>15045</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4033,12 +4033,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>17112</t>
+          <t>16662</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>14744</t>
+          <t>14879</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>28761</t>
+          <t>28894</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -4131,12 +4131,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>579</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>800</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4244,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7344</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18069</t>
+          <t>18877</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14643</t>
+          <t>13533</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>14505</t>
+          <t>14693</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>29900</t>
+          <t>29036</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -4357,12 +4357,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9806</t>
+          <t>9798</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>13988</t>
+          <t>14016</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -5039,12 +5039,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>53528</t>
+          <t>53986</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>79671</t>
+          <t>79574</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>51476</t>
+          <t>51916</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>76842</t>
+          <t>76646</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>112831</t>
+          <t>112153</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>147747</t>
+          <t>147130</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>56353</t>
+          <t>55627</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>81692</t>
+          <t>80211</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>45234</t>
+          <t>43837</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>67576</t>
+          <t>67340</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>106363</t>
+          <t>107726</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>140980</t>
+          <t>141215</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -5265,12 +5265,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>56206</t>
+          <t>56380</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>81588</t>
+          <t>81783</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>57830</t>
+          <t>57448</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>83339</t>
+          <t>83707</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>121289</t>
+          <t>119644</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>155905</t>
+          <t>154215</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -5378,12 +5378,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>62490</t>
+          <t>61427</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>87346</t>
+          <t>87684</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>63451</t>
+          <t>62697</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>89372</t>
+          <t>89373</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>131140</t>
+          <t>131165</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>168845</t>
+          <t>169570</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>27839</t>
+          <t>28057</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>46490</t>
+          <t>48105</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>38037</t>
+          <t>38574</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>60391</t>
+          <t>59730</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>72649</t>
+          <t>72495</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>100077</t>
+          <t>100001</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -5604,12 +5604,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>212752</t>
+          <t>212842</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>251074</t>
+          <t>256568</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5639,12 +5639,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>251294</t>
+          <t>252092</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>295129</t>
+          <t>292870</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>476150</t>
+          <t>472240</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>532254</t>
+          <t>533432</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,04%</t>
         </is>
       </c>
     </row>
@@ -5717,12 +5717,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>100155</t>
+          <t>100168</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>133623</t>
+          <t>131566</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>96426</t>
+          <t>96811</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>127078</t>
+          <t>126422</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>204287</t>
+          <t>202562</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>247500</t>
+          <t>246750</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -5830,12 +5830,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11146</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>24255</t>
+          <t>24410</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5845,12 +5845,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>18300</t>
+          <t>18965</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>33486</t>
+          <t>34086</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>32795</t>
+          <t>33346</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>52976</t>
+          <t>52745</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -5943,12 +5943,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>9342</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5958,39 +5958,39 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>2092</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5610</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>2092</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>5535</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>11432</t>
+          <t>11943</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6028,12 +6028,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -7308,12 +7308,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>67164</t>
+          <t>67573</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>79609</t>
+          <t>79593</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64395</t>
+          <t>64371</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76744</t>
+          <t>76348</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>134879</t>
+          <t>135822</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>152780</t>
+          <t>153445</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -7421,12 +7421,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9165</t>
+          <t>9122</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21420</t>
+          <t>20447</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17950</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19234</t>
+          <t>18986</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35958</t>
+          <t>34121</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -7534,12 +7534,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8186</t>
+          <t>8391</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>882</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>7968</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12690</t>
+          <t>12877</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -7764,12 +7764,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19486</t>
+          <t>18819</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35182</t>
+          <t>35848</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23343</t>
+          <t>22918</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41614</t>
+          <t>40940</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7814,12 +7814,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47257</t>
+          <t>46542</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70680</t>
+          <t>70061</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -8216,12 +8216,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39819</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>63150</t>
+          <t>62305</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8251,12 +8251,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62062</t>
+          <t>61903</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89155</t>
+          <t>89979</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>110855</t>
+          <t>110589</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>144718</t>
+          <t>143873</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -8329,12 +8329,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43273</t>
+          <t>43461</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>66135</t>
+          <t>65995</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8344,12 +8344,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8364,12 +8364,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49766</t>
+          <t>50153</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>73604</t>
+          <t>74969</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>99311</t>
+          <t>98203</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>131386</t>
+          <t>132203</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -8442,12 +8442,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38673</t>
+          <t>39055</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60198</t>
+          <t>60448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45242</t>
+          <t>45974</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69283</t>
+          <t>69964</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90175</t>
+          <t>89039</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>120351</t>
+          <t>121908</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -8555,12 +8555,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>228651</t>
+          <t>227528</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>262869</t>
+          <t>262246</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>218370</t>
+          <t>216840</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>253456</t>
+          <t>255553</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>456423</t>
+          <t>457261</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>505032</t>
+          <t>507327</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,63%</t>
         </is>
       </c>
     </row>
@@ -8668,12 +8668,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17754</t>
+          <t>17452</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33601</t>
+          <t>33315</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8703,12 +8703,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22392</t>
+          <t>21565</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41059</t>
+          <t>38621</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>44474</t>
+          <t>44358</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>67723</t>
+          <t>67437</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8816,12 +8816,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8831,12 +8831,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8851,12 +8851,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8866,12 +8866,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>4568</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>740</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7137</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>9284</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9209,12 +9209,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -9350,12 +9350,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>36822</t>
+          <t>36492</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>56576</t>
+          <t>55450</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9385,12 +9385,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>46513</t>
+          <t>47001</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>68284</t>
+          <t>67941</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9420,12 +9420,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>89637</t>
+          <t>88661</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>115440</t>
+          <t>116767</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9435,12 +9435,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -9463,12 +9463,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>65114</t>
+          <t>66433</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>87702</t>
+          <t>87649</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>53625</t>
+          <t>54770</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>75309</t>
+          <t>75426</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9513,12 +9513,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9533,12 +9533,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>126205</t>
+          <t>125233</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>156159</t>
+          <t>156227</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9548,12 +9548,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,08%</t>
         </is>
       </c>
     </row>
@@ -9576,12 +9576,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9139</t>
+          <t>9213</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>21664</t>
+          <t>21235</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>9801</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>23510</t>
+          <t>22787</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9626,12 +9626,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9646,12 +9646,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>22540</t>
+          <t>22174</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>39908</t>
+          <t>41420</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9661,12 +9661,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -9689,12 +9689,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>13269</t>
+          <t>13951</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>19206</t>
+          <t>19062</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -9739,12 +9739,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -9759,12 +9759,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>13293</t>
+          <t>14721</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>28906</t>
+          <t>29114</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -9774,12 +9774,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13947</t>
+          <t>14109</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9817,12 +9817,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9837,12 +9837,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>11672</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9852,12 +9852,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9872,12 +9872,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>9424</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>21494</t>
+          <t>22488</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9887,12 +9887,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15712</t>
+          <t>16427</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9930,12 +9930,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>18157</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9965,12 +9965,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9985,12 +9985,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>15234</t>
+          <t>14571</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>30781</t>
+          <t>30204</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10000,12 +10000,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>7091</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -10484,12 +10484,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>20920</t>
+          <t>20764</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>37930</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10499,12 +10499,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>26198</t>
+          <t>26410</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>44989</t>
+          <t>46184</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10534,12 +10534,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>50891</t>
+          <t>52046</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>76101</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10569,12 +10569,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>35460</t>
+          <t>35512</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>58286</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10725,12 +10725,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10745,12 +10745,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>44461</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>69816</t>
+          <t>68556</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>86460</t>
+          <t>87687</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>119969</t>
+          <t>121687</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -10823,12 +10823,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>64586</t>
+          <t>63053</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>91557</t>
+          <t>89877</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10838,12 +10838,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10858,12 +10858,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>54183</t>
+          <t>52504</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>78827</t>
+          <t>78495</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>124254</t>
+          <t>122835</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>159901</t>
+          <t>160865</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -10936,12 +10936,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>54107</t>
+          <t>53115</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>78074</t>
+          <t>79794</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10951,12 +10951,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10971,12 +10971,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>77019</t>
+          <t>78111</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>106792</t>
+          <t>107829</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>135937</t>
+          <t>137454</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>177114</t>
+          <t>176374</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -11049,12 +11049,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>48495</t>
+          <t>49763</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>73622</t>
+          <t>74475</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -11064,12 +11064,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -11084,12 +11084,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>59969</t>
+          <t>60512</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>87880</t>
+          <t>87487</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>117367</t>
+          <t>117838</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>155172</t>
+          <t>153968</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -11162,12 +11162,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>45919</t>
+          <t>45341</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>69369</t>
+          <t>68940</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11177,12 +11177,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11197,12 +11197,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>51560</t>
+          <t>50674</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>76533</t>
+          <t>75473</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>101844</t>
+          <t>103576</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>137900</t>
+          <t>138407</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -11275,12 +11275,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>235433</t>
+          <t>234822</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>277274</t>
+          <t>278374</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11290,12 +11290,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11310,12 +11310,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>227502</t>
+          <t>225233</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>269054</t>
+          <t>267482</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>472627</t>
+          <t>471884</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>533089</t>
+          <t>532403</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>85223</t>
+          <t>85782</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>115786</t>
+          <t>116955</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>89729</t>
+          <t>89197</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>119080</t>
+          <t>120057</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>182178</t>
+          <t>181275</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>226891</t>
+          <t>224459</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>10849</t>
+          <t>11083</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>24930</t>
+          <t>26561</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>21663</t>
+          <t>21642</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>23768</t>
+          <t>22886</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>42512</t>
+          <t>42621</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -11614,12 +11614,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2251</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10149</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -11649,12 +11649,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>8657</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>15526</t>
+          <t>15514</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -12979,12 +12979,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41489</t>
+          <t>41539</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52180</t>
+          <t>51923</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12994,12 +12994,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13014,12 +13014,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48970</t>
+          <t>49432</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59592</t>
+          <t>59822</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -13029,12 +13029,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>94639</t>
+          <t>94496</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>109180</t>
+          <t>109772</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -13064,12 +13064,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,73%</t>
         </is>
       </c>
     </row>
@@ -13092,12 +13092,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17203</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13107,12 +13107,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13127,12 +13127,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>15752</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -13142,12 +13142,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13162,12 +13162,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15292</t>
+          <t>15099</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29485</t>
+          <t>29586</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -13177,12 +13177,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -13210,7 +13210,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13275,12 +13275,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7118</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -13295,7 +13295,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -13435,12 +13435,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33754</t>
+          <t>33946</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54775</t>
+          <t>54178</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13450,12 +13450,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30946</t>
+          <t>31170</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51178</t>
+          <t>53315</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13505,12 +13505,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70638</t>
+          <t>70506</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98815</t>
+          <t>98337</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13520,12 +13520,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -13887,12 +13887,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63482</t>
+          <t>62564</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88599</t>
+          <t>89934</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13902,12 +13902,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13922,12 +13922,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72244</t>
+          <t>70716</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>98876</t>
+          <t>99358</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13937,12 +13937,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13957,12 +13957,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>142602</t>
+          <t>141421</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>179960</t>
+          <t>180473</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13972,12 +13972,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -14000,12 +14000,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58562</t>
+          <t>59281</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>83203</t>
+          <t>85160</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14015,12 +14015,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14035,12 +14035,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>63774</t>
+          <t>63505</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>91906</t>
+          <t>91682</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14050,12 +14050,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14070,12 +14070,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>129964</t>
+          <t>130337</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>166713</t>
+          <t>167092</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14085,12 +14085,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -14113,12 +14113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43095</t>
+          <t>42707</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64914</t>
+          <t>65366</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -14128,12 +14128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14148,12 +14148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57391</t>
+          <t>55991</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82366</t>
+          <t>81417</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14163,12 +14163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14183,12 +14183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>106220</t>
+          <t>103831</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>138099</t>
+          <t>138906</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -14198,12 +14198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -14226,12 +14226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>177032</t>
+          <t>180336</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>213779</t>
+          <t>213097</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -14241,12 +14241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -14261,12 +14261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>170344</t>
+          <t>171100</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>204673</t>
+          <t>205196</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -14276,12 +14276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -14296,12 +14296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>357853</t>
+          <t>356725</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>406265</t>
+          <t>404537</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -14311,12 +14311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,13%</t>
         </is>
       </c>
     </row>
@@ -14339,12 +14339,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20927</t>
+          <t>20980</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36594</t>
+          <t>36630</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -14354,12 +14354,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14374,12 +14374,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19801</t>
+          <t>20209</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36897</t>
+          <t>36428</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -14389,12 +14389,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14409,12 +14409,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>44726</t>
+          <t>45322</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>69323</t>
+          <t>68364</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14424,12 +14424,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -14452,12 +14452,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14467,12 +14467,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14487,12 +14487,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5895</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14507,7 +14507,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14522,12 +14522,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12107</t>
+          <t>12575</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14537,12 +14537,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -14565,12 +14565,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>623</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14585,7 +14585,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14635,12 +14635,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>629</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14655,7 +14655,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -14800,7 +14800,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14815,7 +14815,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14830,12 +14830,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14845,12 +14845,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14865,12 +14865,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>10174</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14880,12 +14880,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -15021,12 +15021,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>59667</t>
+          <t>59398</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>81328</t>
+          <t>79833</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15056,12 +15056,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>74753</t>
+          <t>74364</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>97221</t>
+          <t>96439</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -15071,12 +15071,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>138849</t>
+          <t>140523</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>169826</t>
+          <t>173205</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -15106,12 +15106,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>48,18%</t>
         </is>
       </c>
     </row>
@@ -15134,12 +15134,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>49766</t>
+          <t>49497</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>69831</t>
+          <t>70348</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -15149,12 +15149,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -15169,12 +15169,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>50680</t>
+          <t>50183</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>71204</t>
+          <t>71487</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -15184,12 +15184,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -15204,12 +15204,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>105963</t>
+          <t>105011</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>134131</t>
+          <t>135895</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,8%</t>
         </is>
       </c>
     </row>
@@ -15247,12 +15247,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>20201</t>
+          <t>20118</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -15262,12 +15262,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15282,12 +15282,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>19093</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -15297,12 +15297,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15317,12 +15317,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>17397</t>
+          <t>18469</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>33683</t>
+          <t>34416</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -15332,12 +15332,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -15360,12 +15360,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>8022</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>19103</t>
+          <t>18973</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15375,12 +15375,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15395,12 +15395,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>9631</t>
+          <t>10033</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>22337</t>
+          <t>22094</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15410,12 +15410,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15430,12 +15430,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>20174</t>
+          <t>19845</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>37767</t>
+          <t>37365</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -15445,12 +15445,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -15473,12 +15473,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -15488,12 +15488,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8655</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -15523,12 +15523,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15543,12 +15543,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>13619</t>
+          <t>13591</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -15558,12 +15558,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -15586,12 +15586,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13468</t>
+          <t>14359</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -15601,12 +15601,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15621,12 +15621,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>11402</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15636,12 +15636,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -15656,12 +15656,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>9651</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>22329</t>
+          <t>21858</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -15671,12 +15671,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -15699,12 +15699,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>452</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -15719,7 +15719,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15769,12 +15769,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>453</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -16000,7 +16000,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -16015,7 +16015,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -16155,12 +16155,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>34975</t>
+          <t>35416</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>56648</t>
+          <t>55227</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -16170,12 +16170,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -16190,12 +16190,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>34609</t>
+          <t>33889</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>56631</t>
+          <t>56089</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -16205,12 +16205,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -16225,12 +16225,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>74754</t>
+          <t>73300</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>104392</t>
+          <t>103417</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -16240,12 +16240,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>59276</t>
+          <t>57819</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>84410</t>
+          <t>84292</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -16396,12 +16396,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -16416,12 +16416,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>73165</t>
+          <t>72457</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>101180</t>
+          <t>102429</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -16431,12 +16431,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -16451,12 +16451,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>138554</t>
+          <t>139412</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>178152</t>
+          <t>178169</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -16494,12 +16494,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>48154</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>71778</t>
+          <t>73577</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -16509,12 +16509,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -16529,12 +16529,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>49260</t>
+          <t>49593</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>74549</t>
+          <t>73966</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -16544,12 +16544,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -16564,12 +16564,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>103314</t>
+          <t>104084</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>137989</t>
+          <t>136985</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -16607,12 +16607,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>76731</t>
+          <t>74976</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>104140</t>
+          <t>104982</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -16622,12 +16622,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -16642,12 +16642,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>81775</t>
+          <t>81603</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>114053</t>
+          <t>112000</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -16657,12 +16657,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -16677,12 +16677,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>165700</t>
+          <t>165707</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>207866</t>
+          <t>207059</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -16697,7 +16697,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>70569</t>
+          <t>70118</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>99477</t>
+          <t>98343</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -16735,12 +16735,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16755,12 +16755,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>78605</t>
+          <t>78704</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>107729</t>
+          <t>108792</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -16770,12 +16770,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -16790,12 +16790,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>156701</t>
+          <t>156394</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>196815</t>
+          <t>198053</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -16805,12 +16805,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -16833,12 +16833,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>46388</t>
+          <t>47058</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>68707</t>
+          <t>69805</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -16848,12 +16848,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16868,12 +16868,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>59013</t>
+          <t>59057</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>85619</t>
+          <t>85872</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -16883,12 +16883,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>113281</t>
+          <t>112074</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>147398</t>
+          <t>147862</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16918,12 +16918,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -16946,12 +16946,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>184872</t>
+          <t>185034</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>222206</t>
+          <t>222256</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -16961,7 +16961,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -16981,12 +16981,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>173614</t>
+          <t>173860</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>214384</t>
+          <t>214166</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -16996,12 +16996,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>369879</t>
+          <t>370024</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>424817</t>
+          <t>427147</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -17031,12 +17031,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -17059,12 +17059,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>63792</t>
+          <t>63800</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>90292</t>
+          <t>91078</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -17079,7 +17079,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -17094,12 +17094,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>69586</t>
+          <t>68497</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>96867</t>
+          <t>97177</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -17109,12 +17109,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -17129,12 +17129,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>140518</t>
+          <t>141186</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>179011</t>
+          <t>180912</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -17144,12 +17144,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -17172,12 +17172,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>24354</t>
+          <t>24119</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -17187,12 +17187,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -17207,12 +17207,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>7298</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>18927</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -17222,12 +17222,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -17242,12 +17242,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>20246</t>
+          <t>20697</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>38403</t>
+          <t>39663</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -17257,12 +17257,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -17285,12 +17285,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>7482</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -17305,7 +17305,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -17325,7 +17325,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -17340,7 +17340,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -17355,12 +17355,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>11351</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -17370,12 +17370,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -18650,12 +18650,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38264</t>
+          <t>38290</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49081</t>
+          <t>49329</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -18665,12 +18665,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -18685,12 +18685,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44319</t>
+          <t>43874</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55549</t>
+          <t>55995</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -18700,12 +18700,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -18720,12 +18720,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>85279</t>
+          <t>86339</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>102199</t>
+          <t>101807</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -18735,12 +18735,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,25%</t>
         </is>
       </c>
     </row>
@@ -18763,12 +18763,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15233</t>
+          <t>14924</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -18778,12 +18778,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -18798,12 +18798,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15002</t>
+          <t>14883</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -18813,12 +18813,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -18833,12 +18833,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11155</t>
+          <t>11146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27249</t>
+          <t>25200</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -18848,12 +18848,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -18896,7 +18896,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -18911,12 +18911,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>862</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -18926,12 +18926,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -18946,12 +18946,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -19106,12 +19106,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>94082</t>
+          <t>96014</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>192273</t>
+          <t>187607</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -19121,12 +19121,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -19141,12 +19141,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>94979</t>
+          <t>94183</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>147654</t>
+          <t>145804</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -19156,12 +19156,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -19176,12 +19176,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>201609</t>
+          <t>200510</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>306161</t>
+          <t>309970</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -19191,12 +19191,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>416</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -19254,12 +19254,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -19269,12 +19269,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -19289,12 +19289,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12868</t>
+          <t>12394</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -19304,12 +19304,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -19558,12 +19558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>74764</t>
+          <t>74341</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>110219</t>
+          <t>109091</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -19573,12 +19573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -19593,12 +19593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>66700</t>
+          <t>67482</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101258</t>
+          <t>101061</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -19608,12 +19608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -19628,12 +19628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>152794</t>
+          <t>152867</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>203329</t>
+          <t>203103</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -19648,7 +19648,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -19671,12 +19671,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>63443</t>
+          <t>61280</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>96976</t>
+          <t>95502</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -19686,12 +19686,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -19706,12 +19706,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>57186</t>
+          <t>59298</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>91783</t>
+          <t>90713</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -19721,12 +19721,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -19741,12 +19741,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>129588</t>
+          <t>129521</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>174989</t>
+          <t>176818</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -19761,7 +19761,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -19784,12 +19784,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30529</t>
+          <t>29781</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53059</t>
+          <t>51594</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -19799,12 +19799,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -19819,12 +19819,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55434</t>
+          <t>55438</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>83428</t>
+          <t>83049</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -19839,7 +19839,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -19854,12 +19854,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91439</t>
+          <t>90535</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>128200</t>
+          <t>127347</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -19869,12 +19869,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -19897,12 +19897,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92838</t>
+          <t>95864</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>136126</t>
+          <t>137294</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -19912,12 +19912,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -19932,12 +19932,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>138130</t>
+          <t>139911</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>184171</t>
+          <t>182531</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -19947,12 +19947,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -19967,12 +19967,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>251541</t>
+          <t>247499</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>311643</t>
+          <t>309540</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -19982,12 +19982,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,68%</t>
         </is>
       </c>
     </row>
@@ -20010,12 +20010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -20030,7 +20030,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -20045,12 +20045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16117</t>
+          <t>16632</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -20060,12 +20060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -20080,12 +20080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20289</t>
+          <t>19816</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -20095,12 +20095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -20123,12 +20123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>477</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -20138,12 +20138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -20158,12 +20158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>347</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -20178,7 +20178,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -20193,12 +20193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -20213,7 +20213,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -20276,7 +20276,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3541</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -20326,7 +20326,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -20506,7 +20506,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4351</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -20521,7 +20521,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -20541,7 +20541,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -20556,7 +20556,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -20579,12 +20579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20772</t>
+          <t>20339</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -20594,12 +20594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -20614,12 +20614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>12703</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27431</t>
+          <t>27926</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -20629,12 +20629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -20649,12 +20649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>25211</t>
+          <t>24626</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>42923</t>
+          <t>44626</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -20664,12 +20664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -20692,12 +20692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>68488</t>
+          <t>69438</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>89164</t>
+          <t>89236</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -20707,12 +20707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -20727,12 +20727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>91979</t>
+          <t>90440</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>115436</t>
+          <t>115364</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -20742,12 +20742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -20762,12 +20762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>164459</t>
+          <t>166518</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>196065</t>
+          <t>197973</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -20777,12 +20777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>59,47%</t>
         </is>
       </c>
     </row>
@@ -20805,12 +20805,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>43353</t>
+          <t>43968</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>63422</t>
+          <t>61972</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -20820,82 +20820,82 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
+          <t>29,4%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>41,44%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>58539</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>45824</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>70215</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>31,93%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>24,99%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>38,3%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>111433</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>96516</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>126613</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>33,47%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
           <t>28,99%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>42,41%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>58539</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>47241</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>69005</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>31,93%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>25,77%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>37,64%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>111433</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>97431</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>126620</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>33,47%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>29,27%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -20958,7 +20958,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -20973,7 +20973,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -20993,7 +20993,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -21036,7 +21036,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -21051,7 +21051,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -21121,7 +21121,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -21257,12 +21257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>510</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -21277,7 +21277,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -21327,12 +21327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>505</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -21347,7 +21347,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -21375,7 +21375,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -21390,7 +21390,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -21445,7 +21445,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -21460,7 +21460,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -21826,12 +21826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>92745</t>
+          <t>93404</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>195311</t>
+          <t>194431</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -21841,12 +21841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -21861,12 +21861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>93957</t>
+          <t>94479</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>151219</t>
+          <t>150271</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -21876,12 +21876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -21896,12 +21896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>199766</t>
+          <t>201855</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>323799</t>
+          <t>308942</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -21911,12 +21911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -21939,12 +21939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>23332</t>
+          <t>22525</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -21954,12 +21954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -21974,12 +21974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>16975</t>
+          <t>17081</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>34963</t>
+          <t>34305</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -21989,12 +21989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -22009,12 +22009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>31240</t>
+          <t>31480</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>53820</t>
+          <t>52163</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -22024,12 +22024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -22052,12 +22052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>64303</t>
+          <t>63361</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>95848</t>
+          <t>94175</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -22067,12 +22067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -22087,12 +22087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>85977</t>
+          <t>84300</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>126235</t>
+          <t>123240</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -22102,12 +22102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -22122,12 +22122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>157042</t>
+          <t>158994</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>206400</t>
+          <t>207034</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -22137,12 +22137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -22165,12 +22165,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>41326</t>
+          <t>40614</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>66081</t>
+          <t>65489</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -22180,12 +22180,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -22200,12 +22200,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>46768</t>
+          <t>46001</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>74403</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -22215,12 +22215,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -22235,12 +22235,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>94889</t>
+          <t>95445</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>131304</t>
+          <t>130783</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -22250,12 +22250,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -22278,12 +22278,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>77009</t>
+          <t>75975</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>111011</t>
+          <t>110896</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -22293,12 +22293,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -22313,12 +22313,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>70363</t>
+          <t>69582</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>104241</t>
+          <t>104907</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -22328,12 +22328,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -22348,12 +22348,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>154625</t>
+          <t>155580</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>203407</t>
+          <t>202584</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -22363,12 +22363,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -22391,12 +22391,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>63604</t>
+          <t>64875</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>96272</t>
+          <t>96169</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -22406,12 +22406,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -22426,12 +22426,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>60125</t>
+          <t>59276</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>92968</t>
+          <t>90632</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -22441,12 +22441,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -22461,12 +22461,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>131214</t>
+          <t>132047</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>177486</t>
+          <t>178201</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -22476,12 +22476,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -22504,12 +22504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>29735</t>
+          <t>31773</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>51794</t>
+          <t>52611</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -22519,12 +22519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -22539,12 +22539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>54608</t>
+          <t>53631</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>84434</t>
+          <t>83478</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -22554,12 +22554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -22574,12 +22574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>91750</t>
+          <t>90496</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>127591</t>
+          <t>128065</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -22589,12 +22589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -22617,12 +22617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>99893</t>
+          <t>99613</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>138091</t>
+          <t>138386</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -22632,12 +22632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -22652,12 +22652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>138180</t>
+          <t>139247</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>183911</t>
+          <t>189863</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -22667,12 +22667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -22687,12 +22687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>251117</t>
+          <t>251966</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>313341</t>
+          <t>311459</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -22730,12 +22730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>36365</t>
+          <t>36402</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>72500</t>
+          <t>73144</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -22745,12 +22745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -22765,12 +22765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>46947</t>
+          <t>45709</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>73989</t>
+          <t>75013</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -22780,12 +22780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -22800,12 +22800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>88996</t>
+          <t>88388</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>133332</t>
+          <t>136719</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -22815,12 +22815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -22843,12 +22843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>16878</t>
+          <t>17380</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -22858,12 +22858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -22878,12 +22878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>5830</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>18568</t>
+          <t>18478</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -22893,12 +22893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -22913,12 +22913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>13912</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>30894</t>
+          <t>32278</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -22928,12 +22928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -22956,12 +22956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>483</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -22976,7 +22976,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -22991,12 +22991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>7591</t>
+          <t>7752</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -23006,12 +23006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -23026,12 +23026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10331</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -23046,7 +23046,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
